--- a/consent_forms/016_travel_permission_for_minors_form--consent_forms.xlsx
+++ b/consent_forms/016_travel_permission_for_minors_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,17 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parent Info</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Enter parent information</t>
-        </is>
-      </c>
+          <t>Parent Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -552,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travel Info</t>
+          <t>Travel Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -578,11 +574,7 @@
           <t>Trip Details</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Trip duration and destination</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -677,30 +669,30 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_agency_other</t>
+          <t>parent_contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (if applicable)</t>
+          <t>Parent Contact</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -712,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trip_duration</t>
+          <t>other_travel_agency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trip Duration</t>
+          <t>Other Travel Agency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,386 +727,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trip_cost</t>
+          <t>trip_duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trip Cost</t>
+          <t>Trip Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>parent_signature</t>
+          <t>trip_cost</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parent Signature</t>
+          <t>Trip Cost</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>parent_contact</t>
+          <t>parent_signature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Parent Contact</t>
+          <t>Parent Signature</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>travel_agency_contact</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Travel Agency Contact</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other_travel_agency</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Other Contact Info</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>travel_agency_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Travel Agency 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>travel_agency_2_other</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>travel_agency_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Travel Agency 3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>travel_agency_3_other</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>travel_agency_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Travel Agency 4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>travel_agency_4_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>travel_agency_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Travel Agency 5</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>travel_agency_5_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>travel_agency_6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Travel Agency 6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>travel_agency_6_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>travel_agency_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Travel Agency 7</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>travel_agency_7_other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other (if applicable)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1129,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1287,567 +957,6 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Address</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>travel_agency_contact_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>travel_agency_contact_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>travel_agency_contact_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>travel_agency_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>travel_agency_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>travel_agency_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>travel_agency_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>travel_agency_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>travel_agency_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>travel_agency_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>travel_agency_3_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>travel_agency_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>travel_agency_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>travel_agency_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>travel_agency_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>travel_agency_4_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>travel_agency_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>travel_agency_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>travel_agency_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>travel_agency_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>travel_agency_5_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>travel_agency_5_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>travel_agency_5_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>travel_agency_6_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>travel_agency_6_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>travel_agency_6_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>travel_agency_6_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>travel_agency_6_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Southwest</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>travel_agency_7_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>american_airlines</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>travel_agency_7_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>delta_air</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Delta Air</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>travel_agency_7_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>united</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>United</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>travel_agency_7_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>frontier_airlines</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Frontier Airlines</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>travel_agency_7_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>southwest</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Southwest</t>
         </is>
       </c>
     </row>
